--- a/tests/workbooktests/workbooks/test_barrieroptions.xlsx
+++ b/tests/workbooktests/workbooks/test_barrieroptions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04931C4-A1E5-491D-8605-3996F1E203AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BD2914-FC8E-4389-B401-F047FF40FF9C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14775" yWindow="-21315" windowWidth="23040" windowHeight="19740" xr2:uid="{F3283FCA-7801-4C2F-A47C-DC0CACDCB7E5}"/>
   </bookViews>
@@ -34,17 +34,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -53,14 +42,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -441,7 +430,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -501,7 +490,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -517,11 +506,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Market data"/>
       <sheetName val="Calculators"/>
@@ -886,13 +872,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{769DEF14-3DBF-444F-B9C6-BBA2AB834C75}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -900,7 +886,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -909,25 +895,25 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
+      <c r="B4" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
         <v>欣[test_barrieroptions.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlFlatForward(B2,0.02)</f>
+      <c r="B5" t="str">
+        <f>_xll.qlFlatForward(B2,0.02,"actual365fixed")</f>
         <v>欣[test_barrieroptions.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -936,7 +922,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R7C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -944,7 +930,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -953,7 +939,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -961,7 +947,7 @@
         <v>0.19504877171446253</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -969,7 +955,7 @@
         <v>0.39716005835063128</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -977,7 +963,7 @@
         <v>7.5903860839074258E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -985,7 +971,7 @@
         <v>1.3901714719854346</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -993,7 +979,7 @@
         <v>-0.3506856326404631</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -1001,7 +987,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="15">
       <c r="A19" s="4" t="s">
         <v>71</v>
       </c>
@@ -1010,7 +996,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R19C2HestonProcess,A</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="15">
       <c r="A20" s="4" t="s">
         <v>74</v>
       </c>
@@ -1027,13 +1013,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236CE04F-948E-4272-830A-58AA92C8AB49}">
   <dimension ref="A1:D77"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="30.5546875" customWidth="1"/>
-    <col min="2" max="2" width="46.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5" customWidth="1"/>
+    <col min="2" max="2" width="46.5" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1042,7 +1028,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1050,7 +1036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1058,7 +1044,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1066,7 +1052,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1075,7 +1061,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R6C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1084,7 +1070,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R7C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15">
       <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
@@ -1093,7 +1079,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R8C2BarrierOption,A</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1102,7 +1088,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1111,7 +1097,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R11C2AnalyticBarrierEngine,A</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1120,7 +1106,7 @@
         <v>0.79309534207816279</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15">
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
@@ -1129,7 +1115,7 @@
         <v>0.25000925211163788</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1141,7 +1127,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1152,7 +1138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1163,7 +1149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1171,7 +1157,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1179,7 +1165,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1187,7 +1173,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -1198,7 +1184,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -1206,7 +1192,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -1214,7 +1200,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -1222,7 +1208,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1233,7 +1219,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15">
       <c r="A27" s="4" t="s">
         <v>42</v>
       </c>
@@ -1242,7 +1228,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R27C2MCLDBarrierEngine,A</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -1251,12 +1237,12 @@
         <v>0.74753460767823732</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15">
       <c r="A31" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -1265,13 +1251,13 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="B33" s="2">
         <f>B1+180</f>
         <v>46354</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>44</v>
       </c>
@@ -1279,12 +1265,12 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="B35" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -1293,13 +1279,13 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R36C2FixedDividend,A</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="B37" s="3" t="str" cm="1">
         <f t="array" ref="B37">_xll.qlFixedDividend(B35,B33,$B$1)</f>
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R37C2FixedDividend,A</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>62</v>
       </c>
@@ -1311,7 +1297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>73</v>
       </c>
@@ -1320,7 +1306,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R20C2HestonModel,A</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -1328,7 +1314,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -1336,7 +1322,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -1344,7 +1330,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -1352,7 +1338,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>55</v>
       </c>
@@ -1364,7 +1350,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -1372,7 +1358,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -1380,7 +1366,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" ht="15">
       <c r="A49" s="4" t="s">
         <v>46</v>
       </c>
@@ -1389,7 +1375,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R49C2FdBlackScholesBarrierEngine,A</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -1398,7 +1384,7 @@
         <v>0.78155560458039108</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" ht="15">
       <c r="A51" s="4" t="s">
         <v>61</v>
       </c>
@@ -1407,7 +1393,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R51C2FdBlackScholesRebateEngine,A</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -1416,7 +1402,7 @@
         <v>0.29312338986383024</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="15">
       <c r="A54" s="4" t="s">
         <v>72</v>
       </c>
@@ -1425,7 +1411,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R54C2FdHestonBarrierEngine,A</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -1434,7 +1420,7 @@
         <v>1.3020725432013269</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="15">
       <c r="A56" s="4" t="s">
         <v>75</v>
       </c>
@@ -1443,7 +1429,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R56C2FdHestonRebateEngine,A</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1452,7 +1438,7 @@
         <v>0.29376154525479969</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -1461,7 +1447,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>76</v>
       </c>
@@ -1469,7 +1455,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>78</v>
       </c>
@@ -1477,7 +1463,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>79</v>
       </c>
@@ -1486,7 +1472,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R63C2BinomialCRRBarrierEngine,A</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -1495,7 +1481,7 @@
         <v>0.75046203026188807</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -1503,7 +1489,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -1511,7 +1497,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -1519,16 +1505,16 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>117</v>
       </c>
       <c r="B71" s="3" t="str" cm="1">
         <f t="array" ref="B71">_xll.qlCashOrNothingPayoff("Call",100,20,B1)</f>
-        <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R71C2CashOrNothingPayoff,C</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+        <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R71C2CashOrNothingPayoff,A</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -1537,7 +1523,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R72C2AmericanExercise,A</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="15">
       <c r="A73" s="4" t="s">
         <v>13</v>
       </c>
@@ -1546,7 +1532,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R73C2BarrierOption,A</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>62</v>
       </c>
@@ -1555,7 +1541,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="15">
       <c r="A76" s="4" t="s">
         <v>118</v>
       </c>
@@ -1564,7 +1550,7 @@
         <v>欣[test_barrieroptions.xlsx]qlBarrierOption!R76C2AnalyticBinaryBarrierEngine,A</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -1581,13 +1567,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B1192B-2296-4ED6-9D34-2211B52F8221}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" customWidth="1"/>
-    <col min="2" max="2" width="68.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.5" customWidth="1"/>
+    <col min="2" max="2" width="68.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1596,7 +1582,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1604,7 +1590,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1612,7 +1598,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1620,7 +1606,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1629,7 +1615,7 @@
         <v>欣[test_barrieroptions.xlsx]qlQuantoBarrierOption!R6C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1638,7 +1624,7 @@
         <v>欣[test_barrieroptions.xlsx]qlQuantoBarrierOption!R7C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15">
       <c r="A8" s="4" t="s">
         <v>80</v>
       </c>
@@ -1647,7 +1633,7 @@
         <v>欣[test_barrieroptions.xlsx]qlQuantoBarrierOption!R8C2QuantoBarrierOption,A</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1659,19 +1645,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="3" t="str" cm="1">
-        <f t="array" ref="B12">_xll.qlFlatForward(B1,0.02)</f>
-        <v>欣[test_barrieroptions.xlsx]qlQuantoBarrierOption!R12C2YieldTermStructureHandle,I</v>
+      <c r="B12" s="3" t="str">
+        <f>_xll.qlFlatForward(B1,0.02,"actual365fixed")</f>
+        <v>欣[test_barrieroptions.xlsx]qlQuantoBarrierOption!R12C2YieldTermStructureHandle,A</v>
       </c>
       <c r="D12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>83</v>
       </c>
@@ -1683,7 +1669,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -1694,7 +1680,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15">
       <c r="A15" s="4" t="s">
         <v>87</v>
       </c>
@@ -1703,7 +1689,7 @@
         <v>欣[test_barrieroptions.xlsx]qlQuantoBarrierOption!R15C2QuantoBarrierEngine,A</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1720,13 +1706,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3717ED5B-27B3-4EAF-A603-AF025C8D924A}">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="68.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1735,7 +1721,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -1746,7 +1732,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -1757,7 +1743,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -1768,7 +1754,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -1779,7 +1765,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>96</v>
       </c>
@@ -1791,7 +1777,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>98</v>
       </c>
@@ -1803,7 +1789,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15">
       <c r="A9" s="4" t="s">
         <v>101</v>
       </c>
@@ -1812,7 +1798,7 @@
         <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R9C2DoubleBarrierOption,A</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>102</v>
       </c>
@@ -1824,7 +1810,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1833,7 +1819,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -1841,7 +1827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15">
       <c r="A15" s="4" t="s">
         <v>105</v>
       </c>
@@ -1850,7 +1836,7 @@
         <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R15C2AnalyticDoubleBarrierEngine,A</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1859,7 +1845,7 @@
         <v>0.13571870955163434</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15">
       <c r="A17" s="4" t="s">
         <v>115</v>
       </c>
@@ -1868,7 +1854,7 @@
         <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R17C2SuoWangDoubleBarrierEngine,A</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1877,7 +1863,7 @@
         <v>0.13571881151672865</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1886,7 +1872,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -1894,7 +1880,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>78</v>
       </c>
@@ -1902,7 +1888,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15">
       <c r="A23" s="4" t="s">
         <v>116</v>
       </c>
@@ -1911,7 +1897,7 @@
         <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R23C2BinomialCRRDoubleBarrierEngine,A</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -1920,7 +1906,7 @@
         <v>0.19023592715190668</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>106</v>
       </c>
@@ -1932,7 +1918,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -1940,7 +1926,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -1948,7 +1934,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>108</v>
       </c>
@@ -1956,7 +1942,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -1964,7 +1950,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>55</v>
       </c>
@@ -1972,7 +1958,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -1980,7 +1966,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>112</v>
       </c>
@@ -1988,7 +1974,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15">
       <c r="A35" s="4" t="s">
         <v>114</v>
       </c>
@@ -1997,7 +1983,7 @@
         <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R35C2FdHestonDoubleBarrierEngine,A</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -2006,7 +1992,7 @@
         <v>1.5641082865129392</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2014,7 +2000,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2022,7 +2008,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2030,7 +2016,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2038,16 +2024,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>96</v>
       </c>
       <c r="B43" s="3" t="str" cm="1">
         <f t="array" ref="B43">_xll.qlCashOrNothingPayoff("Call",100,20,B1)</f>
-        <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R43C2CashOrNothingPayoff,I</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+        <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R43C2CashOrNothingPayoff,A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2056,7 +2042,7 @@
         <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R44C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15">
       <c r="A45" s="4" t="s">
         <v>101</v>
       </c>
@@ -2065,10 +2051,10 @@
         <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R45C2DoubleBarrierOption,A</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4">
       <c r="B46" s="3"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -2077,7 +2063,7 @@
         <v>欣[test_barrieroptions.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15">
       <c r="A48" s="4" t="s">
         <v>119</v>
       </c>
@@ -2086,7 +2072,7 @@
         <v>欣[test_barrieroptions.xlsx]qlDoubleBarrierOption!R48C2AnalyticDoubleBarrierBinaryEngine,A</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>18</v>
       </c>
